--- a/artfynd/A 31587-2024 artfynd.xlsx
+++ b/artfynd/A 31587-2024 artfynd.xlsx
@@ -2213,7 +2213,7 @@
         <v>135718113</v>
       </c>
       <c r="B17" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>135718207</v>
       </c>
       <c r="B18" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>135718143</v>
       </c>
       <c r="B19" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>135717981</v>
       </c>
       <c r="B20" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>135718186</v>
       </c>
       <c r="B21" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 31587-2024 artfynd.xlsx
+++ b/artfynd/A 31587-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135717979</v>
       </c>
       <c r="B2" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135718002</v>
       </c>
       <c r="B3" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135718042</v>
       </c>
       <c r="B4" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135718084</v>
       </c>
       <c r="B5" t="n">
-        <v>79520</v>
+        <v>79522</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135717434</v>
       </c>
       <c r="B6" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135717617</v>
       </c>
       <c r="B7" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135717944</v>
       </c>
       <c r="B8" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135717995</v>
       </c>
       <c r="B9" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135718060</v>
       </c>
       <c r="B10" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135718085</v>
       </c>
       <c r="B11" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>135718146</v>
       </c>
       <c r="B12" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>135718166</v>
       </c>
       <c r="B13" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>135718190</v>
       </c>
       <c r="B14" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>135718213</v>
       </c>
       <c r="B15" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>135716806</v>
       </c>
       <c r="B16" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>135718113</v>
       </c>
       <c r="B17" t="n">
-        <v>99193</v>
+        <v>99210</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>135718207</v>
       </c>
       <c r="B18" t="n">
-        <v>99193</v>
+        <v>99210</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>135718143</v>
       </c>
       <c r="B19" t="n">
-        <v>99180</v>
+        <v>99197</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>135717981</v>
       </c>
       <c r="B20" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>135718186</v>
       </c>
       <c r="B21" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 31587-2024 artfynd.xlsx
+++ b/artfynd/A 31587-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135717979</v>
       </c>
       <c r="B2" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135718002</v>
       </c>
       <c r="B3" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135718042</v>
       </c>
       <c r="B4" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135718084</v>
       </c>
       <c r="B5" t="n">
-        <v>79522</v>
+        <v>79523</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135717434</v>
       </c>
       <c r="B6" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135717617</v>
       </c>
       <c r="B7" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135717944</v>
       </c>
       <c r="B8" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135717995</v>
       </c>
       <c r="B9" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135718060</v>
       </c>
       <c r="B10" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135718085</v>
       </c>
       <c r="B11" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>135718146</v>
       </c>
       <c r="B12" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>135718166</v>
       </c>
       <c r="B13" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>135718190</v>
       </c>
       <c r="B14" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>135718213</v>
       </c>
       <c r="B15" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>135716806</v>
       </c>
       <c r="B16" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>135718113</v>
       </c>
       <c r="B17" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>135718207</v>
       </c>
       <c r="B18" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>135718143</v>
       </c>
       <c r="B19" t="n">
-        <v>99197</v>
+        <v>99198</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>135717981</v>
       </c>
       <c r="B20" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>135718186</v>
       </c>
       <c r="B21" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 31587-2024 artfynd.xlsx
+++ b/artfynd/A 31587-2024 artfynd.xlsx
@@ -2213,7 +2213,7 @@
         <v>135718113</v>
       </c>
       <c r="B17" t="n">
-        <v>99211</v>
+        <v>99212</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>135718207</v>
       </c>
       <c r="B18" t="n">
-        <v>99211</v>
+        <v>99212</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>135718143</v>
       </c>
       <c r="B19" t="n">
-        <v>99198</v>
+        <v>99199</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>135717981</v>
       </c>
       <c r="B20" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>135718186</v>
       </c>
       <c r="B21" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 31587-2024 artfynd.xlsx
+++ b/artfynd/A 31587-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135717979</v>
       </c>
       <c r="B2" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135718002</v>
       </c>
       <c r="B3" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135718042</v>
       </c>
       <c r="B4" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135718084</v>
       </c>
       <c r="B5" t="n">
-        <v>79523</v>
+        <v>79524</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135717434</v>
       </c>
       <c r="B6" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135717617</v>
       </c>
       <c r="B7" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135717944</v>
       </c>
       <c r="B8" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135717995</v>
       </c>
       <c r="B9" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135718060</v>
       </c>
       <c r="B10" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135718085</v>
       </c>
       <c r="B11" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>135718146</v>
       </c>
       <c r="B12" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>135718166</v>
       </c>
       <c r="B13" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>135718190</v>
       </c>
       <c r="B14" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>135718213</v>
       </c>
       <c r="B15" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>135716806</v>
       </c>
       <c r="B16" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>135718113</v>
       </c>
       <c r="B17" t="n">
-        <v>99212</v>
+        <v>99213</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>135718207</v>
       </c>
       <c r="B18" t="n">
-        <v>99212</v>
+        <v>99213</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>135718143</v>
       </c>
       <c r="B19" t="n">
-        <v>99199</v>
+        <v>99200</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>135717981</v>
       </c>
       <c r="B20" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>135718186</v>
       </c>
       <c r="B21" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 31587-2024 artfynd.xlsx
+++ b/artfynd/A 31587-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135717979</v>
       </c>
       <c r="B2" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135718002</v>
       </c>
       <c r="B3" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135718042</v>
       </c>
       <c r="B4" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135718084</v>
       </c>
       <c r="B5" t="n">
-        <v>79524</v>
+        <v>79528</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135717434</v>
       </c>
       <c r="B6" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135717617</v>
       </c>
       <c r="B7" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135717944</v>
       </c>
       <c r="B8" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135717995</v>
       </c>
       <c r="B9" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135718060</v>
       </c>
       <c r="B10" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135718085</v>
       </c>
       <c r="B11" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>135718146</v>
       </c>
       <c r="B12" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>135718166</v>
       </c>
       <c r="B13" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>135718190</v>
       </c>
       <c r="B14" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>135718213</v>
       </c>
       <c r="B15" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>135716806</v>
       </c>
       <c r="B16" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>135718113</v>
       </c>
       <c r="B17" t="n">
-        <v>99213</v>
+        <v>99219</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>135718207</v>
       </c>
       <c r="B18" t="n">
-        <v>99213</v>
+        <v>99219</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>135718143</v>
       </c>
       <c r="B19" t="n">
-        <v>99200</v>
+        <v>99206</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>135717981</v>
       </c>
       <c r="B20" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>135718186</v>
       </c>
       <c r="B21" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 31587-2024 artfynd.xlsx
+++ b/artfynd/A 31587-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135717979</v>
       </c>
       <c r="B2" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135718002</v>
       </c>
       <c r="B3" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135718042</v>
       </c>
       <c r="B4" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135718084</v>
       </c>
       <c r="B5" t="n">
-        <v>79528</v>
+        <v>79529</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135717434</v>
       </c>
       <c r="B6" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135717617</v>
       </c>
       <c r="B7" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135717944</v>
       </c>
       <c r="B8" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135717995</v>
       </c>
       <c r="B9" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135718060</v>
       </c>
       <c r="B10" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135718085</v>
       </c>
       <c r="B11" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>135718146</v>
       </c>
       <c r="B12" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>135718166</v>
       </c>
       <c r="B13" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>135718190</v>
       </c>
       <c r="B14" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>135718213</v>
       </c>
       <c r="B15" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>135716806</v>
       </c>
       <c r="B16" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>135718113</v>
       </c>
       <c r="B17" t="n">
-        <v>99219</v>
+        <v>99220</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>135718207</v>
       </c>
       <c r="B18" t="n">
-        <v>99219</v>
+        <v>99220</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>135718143</v>
       </c>
       <c r="B19" t="n">
-        <v>99206</v>
+        <v>99207</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>135717981</v>
       </c>
       <c r="B20" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>135718186</v>
       </c>
       <c r="B21" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 31587-2024 artfynd.xlsx
+++ b/artfynd/A 31587-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135717979</v>
       </c>
       <c r="B2" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135718002</v>
       </c>
       <c r="B3" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135718042</v>
       </c>
       <c r="B4" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135718084</v>
       </c>
       <c r="B5" t="n">
-        <v>79529</v>
+        <v>79533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135717434</v>
       </c>
       <c r="B6" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135717617</v>
       </c>
       <c r="B7" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135717944</v>
       </c>
       <c r="B8" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135717995</v>
       </c>
       <c r="B9" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135718060</v>
       </c>
       <c r="B10" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135718085</v>
       </c>
       <c r="B11" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>135718146</v>
       </c>
       <c r="B12" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>135718166</v>
       </c>
       <c r="B13" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>135718190</v>
       </c>
       <c r="B14" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>135718213</v>
       </c>
       <c r="B15" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>135716806</v>
       </c>
       <c r="B16" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>135718113</v>
       </c>
       <c r="B17" t="n">
-        <v>99220</v>
+        <v>99231</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>135718207</v>
       </c>
       <c r="B18" t="n">
-        <v>99220</v>
+        <v>99231</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>135718143</v>
       </c>
       <c r="B19" t="n">
-        <v>99207</v>
+        <v>99218</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>135717981</v>
       </c>
       <c r="B20" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>135718186</v>
       </c>
       <c r="B21" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
